--- a/results/参考工作簿_网点运营总览.xlsx
+++ b/results/参考工作簿_网点运营总览.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08 13:55</t>
+          <t>2026-10-08 15:37</t>
         </is>
       </c>
     </row>
